--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DB512CD-18D4-4733-83DB-7C914C628D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CFB383-E294-4445-A659-850020D3845F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -203,6 +203,15 @@
   </si>
   <si>
     <t>CAP776 S:D1P2631</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>Had a normal day</t>
   </si>
 </sst>
 </file>
@@ -984,7 +993,7 @@
     </row>
     <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>46315</v>
+        <v>46244</v>
       </c>
       <c r="B6" s="9">
         <v>480</v>
@@ -1029,26 +1038,49 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+      <c r="A7" s="8">
+        <v>46245</v>
+      </c>
+      <c r="B7" s="14">
+        <v>480</v>
+      </c>
+      <c r="C7" s="14">
+        <v>45</v>
+      </c>
+      <c r="D7" s="14">
+        <v>120</v>
+      </c>
+      <c r="E7" s="14">
+        <v>90</v>
+      </c>
+      <c r="F7" s="14">
+        <v>180</v>
+      </c>
+      <c r="G7" s="14">
+        <v>5</v>
+      </c>
+      <c r="H7" s="14">
+        <v>60</v>
+      </c>
+      <c r="I7" s="15">
+        <v>975</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>465</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CFB383-E294-4445-A659-850020D3845F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E078A175-68B7-4188-BF99-C1ADA9B6FFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>Had a normal day</t>
+  </si>
+  <si>
+    <t>Totally Hectic day</t>
   </si>
 </sst>
 </file>
@@ -1083,26 +1086,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B8" s="14">
+        <v>480</v>
+      </c>
+      <c r="C8" s="14">
+        <v>45</v>
+      </c>
+      <c r="D8" s="14">
+        <v>120</v>
+      </c>
+      <c r="E8" s="14">
+        <v>90</v>
+      </c>
+      <c r="F8" s="14">
+        <v>400</v>
+      </c>
+      <c r="G8" s="14">
+        <v>8</v>
+      </c>
+      <c r="H8" s="14">
+        <v>60</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1195</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>245</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E078A175-68B7-4188-BF99-C1ADA9B6FFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4046A402-2290-46AF-BFE8-AEECEF5F4E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>Totally Hectic day</t>
+  </si>
+  <si>
+    <t>satisfied</t>
+  </si>
+  <si>
+    <t>had a debate in communication class mam appreciated felt happy</t>
   </si>
 </sst>
 </file>
@@ -1131,27 +1137,51 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+    <row r="9" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B9" s="14">
+        <v>480</v>
+      </c>
+      <c r="C9" s="14">
+        <v>45</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>90</v>
+      </c>
+      <c r="F9" s="14">
+        <v>560</v>
+      </c>
+      <c r="G9" s="14">
+        <v>7</v>
+      </c>
+      <c r="H9" s="14">
+        <v>60</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1355</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>85</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4046A402-2290-46AF-BFE8-AEECEF5F4E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E4676D9-E7F0-4EEC-BF4C-CC60E9552478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>had a debate in communication class mam appreciated felt happy</t>
+  </si>
+  <si>
+    <t>had a normal day</t>
   </si>
 </sst>
 </file>
@@ -1184,26 +1187,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
+      <c r="C10" s="14">
+        <v>30</v>
+      </c>
+      <c r="D10" s="14">
+        <v>120</v>
+      </c>
+      <c r="E10" s="14">
+        <v>90</v>
+      </c>
+      <c r="F10" s="14">
+        <v>150</v>
+      </c>
+      <c r="G10" s="14">
+        <v>3</v>
+      </c>
+      <c r="H10" s="14">
+        <v>120</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E4676D9-E7F0-4EEC-BF4C-CC60E9552478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DFDC80-FB2F-4B75-BB66-5CB7C97EB69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,21 @@
   </si>
   <si>
     <t>had a normal day</t>
+  </si>
+  <si>
+    <t>relaxed</t>
+  </si>
+  <si>
+    <t>watched a lecture of networking feeling great</t>
+  </si>
+  <si>
+    <t>neutral</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">had a normal day </t>
   </si>
 </sst>
 </file>
@@ -1232,49 +1247,97 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B11" s="14">
+        <v>600</v>
+      </c>
+      <c r="C11" s="14">
+        <v>30</v>
+      </c>
+      <c r="D11" s="14">
+        <v>120</v>
+      </c>
+      <c r="E11" s="14">
+        <v>90</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>180</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B12" s="14">
+        <v>600</v>
+      </c>
+      <c r="C12" s="14">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14">
+        <v>180</v>
+      </c>
+      <c r="E12" s="14">
+        <v>90</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>180</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DFDC80-FB2F-4B75-BB66-5CB7C97EB69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910FBA85-8FB5-4B28-80BC-E9299774BC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,15 @@
   </si>
   <si>
     <t xml:space="preserve">had a normal day </t>
+  </si>
+  <si>
+    <t>nuetral</t>
+  </si>
+  <si>
+    <t>feeling low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Had fever and cold </t>
   </si>
 </sst>
 </file>
@@ -1340,26 +1349,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B13" s="14">
+        <v>600</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>180</v>
+      </c>
+      <c r="E13" s="14">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14">
+        <v>300</v>
+      </c>
+      <c r="G13" s="14">
+        <v>5</v>
+      </c>
+      <c r="H13" s="14">
+        <v>60</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910FBA85-8FB5-4B28-80BC-E9299774BC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995982E9-309B-4B1E-89BE-1AB60C207563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,27 @@
   </si>
   <si>
     <t xml:space="preserve">Had fever and cold </t>
+  </si>
+  <si>
+    <t xml:space="preserve">feeling very low </t>
+  </si>
+  <si>
+    <t>not satisfied</t>
+  </si>
+  <si>
+    <t>very low</t>
+  </si>
+  <si>
+    <t>had viral fever</t>
+  </si>
+  <si>
+    <t>vey low</t>
+  </si>
+  <si>
+    <t>ver low</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -1090,7 +1111,7 @@
         <v>90</v>
       </c>
       <c r="F7" s="14">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="G7" s="14">
         <v>5</v>
@@ -1181,7 +1202,7 @@
         <v>90</v>
       </c>
       <c r="F9" s="14">
-        <v>560</v>
+        <v>350</v>
       </c>
       <c r="G9" s="14">
         <v>7</v>
@@ -1191,11 +1212,11 @@
       </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>1355</v>
+        <v>1145</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>85</v>
+        <v>295</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>56</v>
@@ -1365,21 +1386,21 @@
         <v>0</v>
       </c>
       <c r="F13" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G13" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H13" s="14">
         <v>60</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1040</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>69</v>
@@ -1394,93 +1415,189 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B14" s="14">
+        <v>600</v>
+      </c>
+      <c r="C14" s="14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14">
+        <v>0</v>
+      </c>
+      <c r="E14" s="14">
+        <v>0</v>
+      </c>
+      <c r="F14" s="14">
+        <v>250</v>
+      </c>
+      <c r="G14" s="14">
+        <v>5</v>
+      </c>
+      <c r="H14" s="14">
+        <v>60</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B15" s="14">
+        <v>720</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>0</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>350</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
+        <v>60</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B16" s="14">
+        <v>720</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>0</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>250</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="14">
+        <v>60</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B17" s="14">
+        <v>720</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>120</v>
+      </c>
+      <c r="E17" s="14">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14">
+        <v>250</v>
+      </c>
+      <c r="G17" s="14">
+        <v>5</v>
+      </c>
+      <c r="H17" s="14">
+        <v>60</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995982E9-309B-4B1E-89BE-1AB60C207563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F067DE3E-CF09-4249-984A-D1667A538AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">felt bit better today </t>
   </si>
 </sst>
 </file>
@@ -1600,26 +1603,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B18" s="14">
+        <v>720</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>120</v>
+      </c>
+      <c r="E18" s="14">
+        <v>30</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>60</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F067DE3E-CF09-4249-984A-D1667A538AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1470B4-835D-48D8-B28A-FC7A8E586D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t xml:space="preserve">felt bit better today </t>
+  </si>
+  <si>
+    <t>Had a normal Day</t>
   </si>
 </sst>
 </file>
@@ -1649,26 +1652,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B19" s="14">
+        <v>720</v>
+      </c>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>180</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1470B4-835D-48D8-B28A-FC7A8E586D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03DEC59E-7804-4683-BB19-AAEC70DAE433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>Had a normal Day</t>
+  </si>
+  <si>
+    <t>studied dbms</t>
   </si>
 </sst>
 </file>
@@ -1698,26 +1701,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B20" s="14">
+        <v>600</v>
+      </c>
+      <c r="C20" s="14">
+        <v>30</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>30</v>
+      </c>
+      <c r="F20" s="14">
+        <v>100</v>
+      </c>
+      <c r="G20" s="14">
+        <v>2</v>
+      </c>
+      <c r="H20" s="14">
+        <v>120</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03DEC59E-7804-4683-BB19-AAEC70DAE433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C27AC76-BB9B-4270-8533-EB84495902CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1747,26 +1747,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B21" s="14">
+        <v>600</v>
+      </c>
+      <c r="C21" s="14">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14">
+        <v>120</v>
+      </c>
+      <c r="E21" s="14">
+        <v>90</v>
+      </c>
+      <c r="F21" s="14">
+        <v>300</v>
+      </c>
+      <c r="G21" s="14">
+        <v>6</v>
+      </c>
+      <c r="H21" s="14">
+        <v>120</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C27AC76-BB9B-4270-8533-EB84495902CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9EE5EEA-064D-4C43-B7EB-FC60074CF873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,12 @@
   </si>
   <si>
     <t>studied dbms</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>had a stomach ache</t>
   </si>
 </sst>
 </file>
@@ -1793,26 +1799,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B22" s="14">
+        <v>600</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>0</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>400</v>
+      </c>
+      <c r="G22" s="14">
+        <v>8</v>
+      </c>
+      <c r="H22" s="14">
+        <v>120</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9EE5EEA-064D-4C43-B7EB-FC60074CF873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821C9690-303B-4B33-A0DC-0326F8137A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>had a stomach ache</t>
+  </si>
+  <si>
+    <t>studied networking</t>
   </si>
 </sst>
 </file>
@@ -1845,26 +1848,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B23" s="14">
+        <v>600</v>
+      </c>
+      <c r="C23" s="14">
+        <v>0</v>
+      </c>
+      <c r="D23" s="14">
+        <v>120</v>
+      </c>
+      <c r="E23" s="14">
+        <v>30</v>
+      </c>
+      <c r="F23" s="14">
+        <v>250</v>
+      </c>
+      <c r="G23" s="14">
+        <v>5</v>
+      </c>
+      <c r="H23" s="14">
+        <v>120</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821C9690-303B-4B33-A0DC-0326F8137A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3D23AE-81BB-489B-B728-5DA3197258FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1894,26 +1894,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B24" s="14">
+        <v>480</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>30</v>
+      </c>
+      <c r="F24" s="14">
+        <v>250</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>120</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3D23AE-81BB-489B-B728-5DA3197258FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{615032D7-F3AE-466E-ADE8-7E5C9C80D54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1940,26 +1940,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B25" s="14">
+        <v>480</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>60</v>
+      </c>
+      <c r="E25" s="14">
+        <v>0</v>
+      </c>
+      <c r="F25" s="14">
+        <v>60</v>
+      </c>
+      <c r="G25" s="14">
+        <v>1</v>
+      </c>
+      <c r="H25" s="14">
+        <v>240</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{615032D7-F3AE-466E-ADE8-7E5C9C80D54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E176CC47-120F-4EAF-B7C7-D09762033E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1986,26 +1986,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B26" s="14">
+        <v>540</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>180</v>
+      </c>
+      <c r="E26" s="14">
+        <v>60</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>120</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E176CC47-120F-4EAF-B7C7-D09762033E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FC3CCF-018A-4C58-9148-B94EB43FFF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2032,26 +2032,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B27" s="14">
+        <v>540</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>30</v>
+      </c>
+      <c r="F27" s="14">
+        <v>100</v>
+      </c>
+      <c r="G27" s="14">
+        <v>2</v>
+      </c>
+      <c r="H27" s="14">
+        <v>120</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FC3CCF-018A-4C58-9148-B94EB43FFF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67300AAA-2F4F-42FE-B5AD-5EEA09D702B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2078,26 +2078,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B28" s="14">
+        <v>540</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>120</v>
+      </c>
+      <c r="E28" s="14">
+        <v>30</v>
+      </c>
+      <c r="F28" s="14">
+        <v>400</v>
+      </c>
+      <c r="G28" s="14">
+        <v>8</v>
+      </c>
+      <c r="H28" s="14">
+        <v>120</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67300AAA-2F4F-42FE-B5AD-5EEA09D702B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A875D9-5B27-4BBC-9135-7045426D71B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>studied networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neutral </t>
   </si>
 </sst>
 </file>
@@ -2094,21 +2097,21 @@
         <v>30</v>
       </c>
       <c r="F28" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H28" s="14">
         <v>120</v>
       </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>1210</v>
+        <v>1110</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>230</v>
+        <v>330</v>
       </c>
       <c r="K28" s="16" t="s">
         <v>56</v>
@@ -2124,26 +2127,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B29" s="14">
+        <v>480</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>0</v>
+      </c>
+      <c r="E29" s="14">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>400</v>
+      </c>
+      <c r="G29" s="14">
+        <v>8</v>
+      </c>
+      <c r="H29" s="14">
+        <v>180</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A875D9-5B27-4BBC-9135-7045426D71B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE63706-03EE-4C70-83A8-19B738749612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -229,9 +229,6 @@
     <t>relaxed</t>
   </si>
   <si>
-    <t>watched a lecture of networking feeling great</t>
-  </si>
-  <si>
     <t>neutral</t>
   </si>
   <si>
@@ -271,9 +268,6 @@
     <t>Low</t>
   </si>
   <si>
-    <t xml:space="preserve">felt bit better today </t>
-  </si>
-  <si>
     <t>Had a normal Day</t>
   </si>
   <si>
@@ -290,6 +284,15 @@
   </si>
   <si>
     <t xml:space="preserve">neutral </t>
+  </si>
+  <si>
+    <t xml:space="preserve">watched a lecture of networking </t>
+  </si>
+  <si>
+    <t>felt bit better today +tworking  g ng ing king rking orking working N18</t>
+  </si>
+  <si>
+    <t>felt ver low</t>
   </si>
 </sst>
 </file>
@@ -1298,7 +1301,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
         <v>46249</v>
       </c>
@@ -1341,7 +1344,7 @@
         <v>57</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1381,13 +1384,13 @@
         <v>63</v>
       </c>
       <c r="L12" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M12" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M12" s="16" t="s">
+      <c r="N12" s="17" t="s">
         <v>66</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1424,16 +1427,16 @@
         <v>400</v>
       </c>
       <c r="K13" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N13" s="17" t="s">
         <v>69</v>
-      </c>
-      <c r="L13" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1470,16 +1473,16 @@
         <v>530</v>
       </c>
       <c r="K14" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L14" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="L14" s="16" t="s">
+      <c r="M14" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="M14" s="16" t="s">
+      <c r="N14" s="17" t="s">
         <v>73</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1516,16 +1519,16 @@
         <v>310</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L15" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M15" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="M15" s="16" t="s">
+      <c r="N15" s="17" t="s">
         <v>73</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1562,16 +1565,16 @@
         <v>410</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L16" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M16" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="M16" s="16" t="s">
+      <c r="N16" s="17" t="s">
         <v>73</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1608,19 +1611,19 @@
         <v>290</v>
       </c>
       <c r="K17" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N17" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="L17" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="M17" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
         <v>46256</v>
       </c>
@@ -1654,16 +1657,16 @@
         <v>480</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L18" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M18" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M18" s="16" t="s">
-        <v>66</v>
-      </c>
       <c r="N18" s="17" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1703,13 +1706,13 @@
         <v>56</v>
       </c>
       <c r="L19" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M19" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M19" s="16" t="s">
-        <v>66</v>
-      </c>
       <c r="N19" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1749,13 +1752,13 @@
         <v>56</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M20" s="16" t="s">
         <v>57</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1795,10 +1798,10 @@
         <v>56</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N21" s="17" t="s">
         <v>62</v>
@@ -1838,16 +1841,16 @@
         <v>320</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1887,13 +1890,13 @@
         <v>56</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M23" s="16" t="s">
         <v>57</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1933,7 +1936,7 @@
         <v>56</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M24" s="16" t="s">
         <v>57</v>
@@ -1979,7 +1982,7 @@
         <v>56</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M25" s="16" t="s">
         <v>57</v>
@@ -2025,7 +2028,7 @@
         <v>56</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M26" s="16" t="s">
         <v>57</v>
@@ -2071,7 +2074,7 @@
         <v>56</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M27" s="16" t="s">
         <v>57</v>
@@ -2117,10 +2120,10 @@
         <v>56</v>
       </c>
       <c r="L28" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M28" s="16" t="s">
         <v>65</v>
-      </c>
-      <c r="M28" s="16" t="s">
-        <v>66</v>
       </c>
       <c r="N28" s="17" t="s">
         <v>62</v>
@@ -2163,102 +2166,198 @@
         <v>56</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N29" s="17" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B30" s="14">
+        <v>480</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>120</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>250</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>120</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B31" s="14">
+        <v>480</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>120</v>
+      </c>
+      <c r="E31" s="14">
+        <v>30</v>
+      </c>
+      <c r="F31" s="14">
+        <v>300</v>
+      </c>
+      <c r="G31" s="14">
+        <v>6</v>
+      </c>
+      <c r="H31" s="14">
+        <v>120</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B32" s="14">
+        <v>600</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>360</v>
+      </c>
+      <c r="E32" s="14">
+        <v>30</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>120</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B33" s="14">
+        <v>600</v>
+      </c>
+      <c r="C33" s="14">
+        <v>0</v>
+      </c>
+      <c r="D33" s="14">
+        <v>240</v>
+      </c>
+      <c r="E33" s="14">
+        <v>0</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>180</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE63706-03EE-4C70-83A8-19B738749612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C83D50-D61D-412E-A4E4-5950332D78D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -292,7 +292,7 @@
     <t>felt bit better today +tworking  g ng ing king rking orking working N18</t>
   </si>
   <si>
-    <t>felt ver low</t>
+    <t>felt very low</t>
   </si>
 </sst>
 </file>
@@ -2350,7 +2350,7 @@
         <v>65</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M33" s="16" t="s">
         <v>57</v>
@@ -2360,26 +2360,50 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B34" s="14">
+        <v>480</v>
+      </c>
+      <c r="C34" s="14">
+        <v>0</v>
+      </c>
+      <c r="D34" s="14">
+        <v>180</v>
+      </c>
+      <c r="E34" s="14">
+        <v>0</v>
+      </c>
+      <c r="F34" s="14">
+        <v>100</v>
+      </c>
+      <c r="G34" s="14">
+        <v>2</v>
+      </c>
+      <c r="H34" s="14">
+        <v>120</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C83D50-D61D-412E-A4E4-5950332D78D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDD17E7-63AA-4480-9EFE-2331F76F595F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>felt very low</t>
+  </si>
+  <si>
+    <t>felt low after the last class</t>
   </si>
 </sst>
 </file>
@@ -2406,26 +2409,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B35" s="14">
+        <v>480</v>
+      </c>
+      <c r="C35" s="14">
+        <v>0</v>
+      </c>
+      <c r="D35" s="14">
+        <v>240</v>
+      </c>
+      <c r="E35" s="14">
+        <v>0</v>
+      </c>
+      <c r="F35" s="14">
+        <v>300</v>
+      </c>
+      <c r="G35" s="14">
+        <v>6</v>
+      </c>
+      <c r="H35" s="14">
+        <v>60</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDD17E7-63AA-4480-9EFE-2331F76F595F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935947F3-7A14-4220-8323-A066C8C5C8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2455,48 +2455,96 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B36" s="14">
+        <v>480</v>
+      </c>
+      <c r="C36" s="14">
+        <v>0</v>
+      </c>
+      <c r="D36" s="14">
+        <v>120</v>
+      </c>
+      <c r="E36" s="14">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
+        <v>400</v>
+      </c>
+      <c r="G36" s="14">
+        <v>8</v>
+      </c>
+      <c r="H36" s="14">
+        <v>120</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B37" s="14">
+        <v>480</v>
+      </c>
+      <c r="C37" s="14">
+        <v>0</v>
+      </c>
+      <c r="D37" s="14">
+        <v>420</v>
+      </c>
+      <c r="E37" s="14">
+        <v>120</v>
+      </c>
+      <c r="F37" s="14">
+        <v>250</v>
+      </c>
+      <c r="G37" s="14">
+        <v>5</v>
+      </c>
+      <c r="H37" s="14">
+        <v>120</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artim\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA\Semester 1\python\My data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935947F3-7A14-4220-8323-A066C8C5C8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC8BF32-4765-4E28-B3ED-738FF28C0602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>felt low after the last class</t>
+  </si>
+  <si>
+    <t>Neutral</t>
   </si>
 </sst>
 </file>
@@ -2547,26 +2550,50 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B38" s="14">
+        <v>480</v>
+      </c>
+      <c r="C38" s="14">
+        <v>0</v>
+      </c>
+      <c r="D38" s="14">
+        <v>120</v>
+      </c>
+      <c r="E38" s="14">
+        <v>30</v>
+      </c>
+      <c r="F38" s="14">
+        <v>300</v>
+      </c>
+      <c r="G38" s="14">
+        <v>6</v>
+      </c>
+      <c r="H38" s="14">
+        <v>120</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA\Semester 1\python\My data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC8BF32-4765-4E28-B3ED-738FF28C0602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4971102-E061-43D0-A0CD-E3767441E2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2596,70 +2596,142 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B39" s="14">
+        <v>480</v>
+      </c>
+      <c r="C39" s="14">
+        <v>0</v>
+      </c>
+      <c r="D39" s="14">
+        <v>120</v>
+      </c>
+      <c r="E39" s="14">
+        <v>30</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>120</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>690</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B40" s="14">
+        <v>480</v>
+      </c>
+      <c r="C40" s="14">
+        <v>0</v>
+      </c>
+      <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
+        <v>30</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>180</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B41" s="14">
+        <v>480</v>
+      </c>
+      <c r="C41" s="14">
+        <v>0</v>
+      </c>
+      <c r="D41" s="14">
+        <v>120</v>
+      </c>
+      <c r="E41" s="14">
+        <v>30</v>
+      </c>
+      <c r="F41" s="14">
+        <v>100</v>
+      </c>
+      <c r="G41" s="14">
+        <v>2</v>
+      </c>
+      <c r="H41" s="14">
+        <v>180</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA\Semester 1\python\My data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4971102-E061-43D0-A0CD-E3767441E2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D538AB3-43DE-4EBC-A012-1502A333564B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>Neutral</t>
+  </si>
+  <si>
+    <t>felt low today</t>
   </si>
 </sst>
 </file>
@@ -2734,114 +2737,234 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B42" s="14">
+        <v>480</v>
+      </c>
+      <c r="C42" s="14">
+        <v>0</v>
+      </c>
+      <c r="D42" s="14">
+        <v>120</v>
+      </c>
+      <c r="E42" s="14">
+        <v>30</v>
+      </c>
+      <c r="F42" s="14">
+        <v>300</v>
+      </c>
+      <c r="G42" s="14">
+        <v>6</v>
+      </c>
+      <c r="H42" s="14">
+        <v>180</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B43" s="14">
+        <v>480</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <v>120</v>
+      </c>
+      <c r="E43" s="14">
+        <v>30</v>
+      </c>
+      <c r="F43" s="14">
+        <v>400</v>
+      </c>
+      <c r="G43" s="14">
+        <v>8</v>
+      </c>
+      <c r="H43" s="14">
+        <v>120</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B44" s="14">
+        <v>480</v>
+      </c>
+      <c r="C44" s="14">
+        <v>0</v>
+      </c>
+      <c r="D44" s="14">
+        <v>180</v>
+      </c>
+      <c r="E44" s="14">
+        <v>30</v>
+      </c>
+      <c r="F44" s="14">
+        <v>250</v>
+      </c>
+      <c r="G44" s="14">
+        <v>5</v>
+      </c>
+      <c r="H44" s="14">
+        <v>120</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B45" s="14">
+        <v>480</v>
+      </c>
+      <c r="C45" s="14">
+        <v>0</v>
+      </c>
+      <c r="D45" s="14">
+        <v>180</v>
+      </c>
+      <c r="E45" s="14">
+        <v>30</v>
+      </c>
+      <c r="F45" s="14">
+        <v>300</v>
+      </c>
+      <c r="G45" s="14">
+        <v>6</v>
+      </c>
+      <c r="H45" s="14">
+        <v>120</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B46" s="14">
+        <v>480</v>
+      </c>
+      <c r="C46" s="14">
+        <v>0</v>
+      </c>
+      <c r="D46" s="14">
+        <v>240</v>
+      </c>
+      <c r="E46" s="14">
+        <v>60</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>120</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA\Semester 1\python\My data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D538AB3-43DE-4EBC-A012-1502A333564B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3713E923-5254-46B3-8191-7BB33E678A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2967,26 +2967,50 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B47" s="14">
+        <v>480</v>
+      </c>
+      <c r="C47" s="14">
+        <v>0</v>
+      </c>
+      <c r="D47" s="14">
+        <v>180</v>
+      </c>
+      <c r="E47" s="14">
+        <v>60</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>120</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>

--- a/Daily_Routine_.xlsx
+++ b/Daily_Routine_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA\Semester 1\python\My data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3713E923-5254-46B3-8191-7BB33E678A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1423B7AE-D32E-49FA-9076-C38174C375C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3013,48 +3013,96 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B48" s="14">
+        <v>480</v>
+      </c>
+      <c r="C48" s="14">
+        <v>0</v>
+      </c>
+      <c r="D48" s="14">
+        <v>180</v>
+      </c>
+      <c r="E48" s="14">
+        <v>60</v>
+      </c>
+      <c r="F48" s="14">
+        <v>100</v>
+      </c>
+      <c r="G48" s="14">
+        <v>2</v>
+      </c>
+      <c r="H48" s="14">
+        <v>120</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B49" s="14">
+        <v>480</v>
+      </c>
+      <c r="C49" s="14">
+        <v>0</v>
+      </c>
+      <c r="D49" s="14">
+        <v>180</v>
+      </c>
+      <c r="E49" s="14">
+        <v>60</v>
+      </c>
+      <c r="F49" s="14">
+        <v>300</v>
+      </c>
+      <c r="G49" s="14">
+        <v>6</v>
+      </c>
+      <c r="H49" s="14">
+        <v>120</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
